--- a/KURIKULUM2026_REVISI/009B_CPL_KETERAMPILAN_UMUM_SISTEKIN.xlsx
+++ b/KURIKULUM2026_REVISI/009B_CPL_KETERAMPILAN_UMUM_SISTEKIN.xlsx
@@ -556,7 +556,7 @@
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
     <col width="69" customWidth="1" min="2" max="2"/>
-    <col width="67.84999999999999" customWidth="1" min="3" max="3"/>
+    <col width="69" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="27.6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Analisis data pada MK Riset Operasi / Data Analytics.</t>
+          <t>Analisis data pada MK Data Mining &amp; Visualisasi / Decision Support Systems.</t>
         </is>
       </c>
     </row>
